--- a/analysis/econometrics_outputs/sdid/Graficos/unemployment/sdid_eventstudy_cosine_weighted_top_vs_zero.xlsx
+++ b/analysis/econometrics_outputs/sdid/Graficos/unemployment/sdid_eventstudy_cosine_weighted_top_vs_zero.xlsx
@@ -507,13 +507,13 @@
         <v>7.143494137888768</v>
       </c>
       <c r="I2" t="n">
-        <v>0.023775170831032</v>
+        <v>0.02860716509716501</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.04659541302090785</v>
+        <v>-0.05606612178252855</v>
       </c>
       <c r="K2" t="n">
-        <v>0.04660325663673758</v>
+        <v>0.05607396539835828</v>
       </c>
     </row>
     <row r="3">
@@ -550,13 +550,13 @@
         <v>7.147143347946397</v>
       </c>
       <c r="I3" t="n">
-        <v>0.023775170831032</v>
+        <v>0.02860716509716501</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.0465963079317253</v>
+        <v>-0.056067016693346</v>
       </c>
       <c r="K3" t="n">
-        <v>0.04660236172592013</v>
+        <v>0.05607307048754083</v>
       </c>
     </row>
     <row r="4">
@@ -593,13 +593,13 @@
         <v>7.133707662794738</v>
       </c>
       <c r="I4" t="n">
-        <v>0.023775170831032</v>
+        <v>0.02860716509716501</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.04658792086797336</v>
+        <v>-0.05605862962959406</v>
       </c>
       <c r="K4" t="n">
-        <v>0.04661074878967208</v>
+        <v>0.05608145755129278</v>
       </c>
     </row>
     <row r="5">
@@ -636,13 +636,13 @@
         <v>7.114353979997055</v>
       </c>
       <c r="I5" t="n">
-        <v>0.023775170831032</v>
+        <v>0.02860716509716501</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.04659811415520453</v>
+        <v>-0.05606882291682523</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0466005555024409</v>
+        <v>0.0560712642640616</v>
       </c>
     </row>
     <row r="6">
@@ -679,13 +679,13 @@
         <v>7.078860145819582</v>
       </c>
       <c r="I6" t="n">
-        <v>0.023775170831032</v>
+        <v>0.02860716509716501</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.04659700645142161</v>
+        <v>-0.05606771521304231</v>
       </c>
       <c r="K6" t="n">
-        <v>0.04660166320622382</v>
+        <v>0.05607237196784452</v>
       </c>
     </row>
     <row r="7">
@@ -722,13 +722,13 @@
         <v>7.047498083327357</v>
       </c>
       <c r="I7" t="n">
-        <v>0.023775170831032</v>
+        <v>0.02860716509716501</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.04659094369576765</v>
+        <v>-0.05606165245738835</v>
       </c>
       <c r="K7" t="n">
-        <v>0.04660772596187778</v>
+        <v>0.05607843472349848</v>
       </c>
     </row>
     <row r="8">
@@ -765,13 +765,13 @@
         <v>7.016173090253348</v>
       </c>
       <c r="I8" t="n">
-        <v>0.023775170831032</v>
+        <v>0.02860716509716501</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.04659854736749191</v>
+        <v>-0.05606925612911261</v>
       </c>
       <c r="K8" t="n">
-        <v>0.04660012229015353</v>
+        <v>0.05607083105177423</v>
       </c>
     </row>
     <row r="9">
@@ -808,13 +808,13 @@
         <v>7.00740932089789</v>
       </c>
       <c r="I9" t="n">
-        <v>0.023775170831032</v>
+        <v>0.02860716509716501</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.04659343635764545</v>
+        <v>-0.05606414511926615</v>
       </c>
       <c r="K9" t="n">
-        <v>0.04660523329999999</v>
+        <v>0.05607594206162068</v>
       </c>
     </row>
     <row r="10">
@@ -851,13 +851,13 @@
         <v>6.974505142875418</v>
       </c>
       <c r="I10" t="n">
-        <v>0.023775170831032</v>
+        <v>0.02860716509716501</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.04659460515165369</v>
+        <v>-0.05606531391327439</v>
       </c>
       <c r="K10" t="n">
-        <v>0.04660406450599174</v>
+        <v>0.05607477326761244</v>
       </c>
     </row>
     <row r="11">
@@ -894,13 +894,13 @@
         <v>6.955527058537186</v>
       </c>
       <c r="I11" t="n">
-        <v>0.023775170831032</v>
+        <v>0.02860716509716501</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.04659099288477785</v>
+        <v>-0.05606170164639855</v>
       </c>
       <c r="K11" t="n">
-        <v>0.04660767677286758</v>
+        <v>0.05607838553448828</v>
       </c>
     </row>
     <row r="12">
@@ -937,13 +937,13 @@
         <v>6.928417635834625</v>
       </c>
       <c r="I12" t="n">
-        <v>0.023775170831032</v>
+        <v>0.02860716509716501</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.04659461086324933</v>
+        <v>-0.05606531962487003</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0466040587943961</v>
+        <v>0.0560747675560168</v>
       </c>
     </row>
     <row r="13">
@@ -980,13 +980,13 @@
         <v>6.899612613809318</v>
       </c>
       <c r="I13" t="n">
-        <v>0.023775170831032</v>
+        <v>0.02860716509716501</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.04660225061844225</v>
+        <v>-0.05607295938006295</v>
       </c>
       <c r="K13" t="n">
-        <v>0.04659641903920319</v>
+        <v>0.05606712780082389</v>
       </c>
     </row>
     <row r="14">
@@ -1023,13 +1023,13 @@
         <v>6.907681402022805</v>
       </c>
       <c r="I14" t="n">
-        <v>0.023775170831032</v>
+        <v>0.02860716509716501</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.04658702811904435</v>
+        <v>-0.05605773688066505</v>
       </c>
       <c r="K14" t="n">
-        <v>0.04661164153860108</v>
+        <v>0.05608235030022178</v>
       </c>
     </row>
     <row r="15">
@@ -1066,13 +1066,13 @@
         <v>6.88986849628777</v>
       </c>
       <c r="I15" t="n">
-        <v>0.023775170831032</v>
+        <v>0.02860716509716501</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.04659657400173222</v>
+        <v>-0.05606728276335292</v>
       </c>
       <c r="K15" t="n">
-        <v>0.04660209565591322</v>
+        <v>0.05607280441753391</v>
       </c>
     </row>
     <row r="16">
@@ -1109,13 +1109,13 @@
         <v>6.878651728246825</v>
       </c>
       <c r="I16" t="n">
-        <v>0.023775170831032</v>
+        <v>0.02860716509716501</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.04659503209918169</v>
+        <v>-0.05606574086080239</v>
       </c>
       <c r="K16" t="n">
-        <v>0.04660363755846374</v>
+        <v>0.05607434632008444</v>
       </c>
     </row>
     <row r="17">
@@ -1152,13 +1152,13 @@
         <v>6.849672412668123</v>
       </c>
       <c r="I17" t="n">
-        <v>0.023775170831032</v>
+        <v>0.02860716509716501</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.04659492610181348</v>
+        <v>-0.05606563486343417</v>
       </c>
       <c r="K17" t="n">
-        <v>0.04660374355583196</v>
+        <v>0.05607445231745266</v>
       </c>
     </row>
     <row r="18">
@@ -1195,13 +1195,13 @@
         <v>6.820501297855685</v>
       </c>
       <c r="I18" t="n">
-        <v>0.023775170831032</v>
+        <v>0.02860716509716501</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.04659427012915151</v>
+        <v>-0.05606497889077221</v>
       </c>
       <c r="K18" t="n">
-        <v>0.04660439952849393</v>
+        <v>0.05607510829011463</v>
       </c>
     </row>
     <row r="19">
@@ -1238,13 +1238,13 @@
         <v>6.807360183018594</v>
       </c>
       <c r="I19" t="n">
-        <v>0.023775170831032</v>
+        <v>0.02860716509716501</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.04659886894572351</v>
+        <v>-0.05606957770734421</v>
       </c>
       <c r="K19" t="n">
-        <v>0.04659980071192193</v>
+        <v>0.05607050947354263</v>
       </c>
     </row>
     <row r="20">
@@ -1281,13 +1281,13 @@
         <v>6.835856398364068</v>
       </c>
       <c r="I20" t="n">
-        <v>0.023775170831032</v>
+        <v>0.02860716509716501</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.0465863464455054</v>
+        <v>-0.0560570552071261</v>
       </c>
       <c r="K20" t="n">
-        <v>0.04661232321214003</v>
+        <v>0.05608303197376073</v>
       </c>
     </row>
     <row r="21">
@@ -1324,13 +1324,13 @@
         <v>6.858921874755683</v>
       </c>
       <c r="I21" t="n">
-        <v>0.023775170831032</v>
+        <v>0.02860716509716501</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.04659933482882272</v>
+        <v>-0.05607004359044342</v>
       </c>
       <c r="K21" t="n">
-        <v>0.04659933482882272</v>
+        <v>0.05607004359044342</v>
       </c>
     </row>
     <row r="22">
@@ -1367,13 +1367,13 @@
         <v>6.837047353119154</v>
       </c>
       <c r="I22" t="n">
-        <v>0.023775170831032</v>
+        <v>0.02860716509716501</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.03631741439273805</v>
+        <v>-0.04578812315435875</v>
       </c>
       <c r="K22" t="n">
-        <v>0.05688125526490739</v>
+        <v>0.06635196402652808</v>
       </c>
     </row>
     <row r="23">
@@ -1410,13 +1410,13 @@
         <v>6.827210393763395</v>
       </c>
       <c r="I23" t="n">
-        <v>0.023775170831032</v>
+        <v>0.02860716509716501</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.02637540905798352</v>
+        <v>-0.03584611781960421</v>
       </c>
       <c r="K23" t="n">
-        <v>0.06682326059966193</v>
+        <v>0.07629396936128262</v>
       </c>
     </row>
     <row r="24">
@@ -1453,13 +1453,13 @@
         <v>6.819310755174234</v>
       </c>
       <c r="I24" t="n">
-        <v>0.023775170831032</v>
+        <v>0.02860716509716501</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.02569560803008274</v>
+        <v>-0.03516631679170344</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0675030616275627</v>
+        <v>0.07697377038918339</v>
       </c>
     </row>
     <row r="25">
@@ -1496,13 +1496,13 @@
         <v>6.804921446601844</v>
       </c>
       <c r="I25" t="n">
-        <v>0.023775170831032</v>
+        <v>0.02860716509716501</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.01829504664413383</v>
+        <v>-0.02776575540575453</v>
       </c>
       <c r="K25" t="n">
-        <v>0.07490362301351161</v>
+        <v>0.0843743317751323</v>
       </c>
     </row>
     <row r="26">
@@ -1539,13 +1539,13 @@
         <v>6.832986813162061</v>
       </c>
       <c r="I26" t="n">
-        <v>0.023775170831032</v>
+        <v>0.02860716509716501</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.02433778509360773</v>
+        <v>-0.03380849385522842</v>
       </c>
       <c r="K26" t="n">
-        <v>0.06886088456403772</v>
+        <v>0.07833159332565841</v>
       </c>
     </row>
     <row r="27">
@@ -1582,13 +1582,13 @@
         <v>6.824299820508662</v>
       </c>
       <c r="I27" t="n">
-        <v>0.023775170831032</v>
+        <v>0.02860716509716501</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.01416078323020175</v>
+        <v>-0.02363149199182245</v>
       </c>
       <c r="K27" t="n">
-        <v>0.07903788642744369</v>
+        <v>0.08850859518906438</v>
       </c>
     </row>
     <row r="28">
@@ -1625,13 +1625,13 @@
         <v>6.793843711629481</v>
       </c>
       <c r="I28" t="n">
-        <v>0.023775170831032</v>
+        <v>0.02860716509716501</v>
       </c>
       <c r="J28" t="n">
-        <v>0.00852463501161372</v>
+        <v>-0.0009460737500069788</v>
       </c>
       <c r="K28" t="n">
-        <v>0.1017233046692592</v>
+        <v>0.1111940134308799</v>
       </c>
     </row>
     <row r="29">
@@ -1668,13 +1668,13 @@
         <v>6.77235016771745</v>
       </c>
       <c r="I29" t="n">
-        <v>0.023775170831032</v>
+        <v>0.02860716509716501</v>
       </c>
       <c r="J29" t="n">
-        <v>0.005076815162342159</v>
+        <v>-0.004393893599278539</v>
       </c>
       <c r="K29" t="n">
-        <v>0.0982754848199876</v>
+        <v>0.1077461935816083</v>
       </c>
     </row>
     <row r="30">
@@ -1711,13 +1711,13 @@
         <v>6.760430696919773</v>
       </c>
       <c r="I30" t="n">
-        <v>0.023775170831032</v>
+        <v>0.02860716509716501</v>
       </c>
       <c r="J30" t="n">
-        <v>0.004975889155745657</v>
+        <v>-0.004494819605875042</v>
       </c>
       <c r="K30" t="n">
-        <v>0.0981745588133911</v>
+        <v>0.1076452675750118</v>
       </c>
     </row>
     <row r="31">
@@ -1754,13 +1754,13 @@
         <v>6.755819906146019</v>
       </c>
       <c r="I31" t="n">
-        <v>0.023775170831032</v>
+        <v>0.02860716509716501</v>
       </c>
       <c r="J31" t="n">
-        <v>0.01042944900820531</v>
+        <v>0.0009587402465846134</v>
       </c>
       <c r="K31" t="n">
-        <v>0.1036281186658508</v>
+        <v>0.1130988274274714</v>
       </c>
     </row>
     <row r="32">
@@ -1797,13 +1797,13 @@
         <v>6.779495036993018</v>
       </c>
       <c r="I32" t="n">
-        <v>0.023775170831032</v>
+        <v>0.02860716509716501</v>
       </c>
       <c r="J32" t="n">
-        <v>0.008560401895718835</v>
+        <v>-0.0009103068659018637</v>
       </c>
       <c r="K32" t="n">
-        <v>0.1017590715533643</v>
+        <v>0.111229780314985</v>
       </c>
     </row>
     <row r="33">
@@ -1840,13 +1840,13 @@
         <v>6.791536491586684</v>
       </c>
       <c r="I33" t="n">
-        <v>0.023775170831032</v>
+        <v>0.02860716509716501</v>
       </c>
       <c r="J33" t="n">
-        <v>0.01812354855352561</v>
+        <v>0.008652839791904912</v>
       </c>
       <c r="K33" t="n">
-        <v>0.1113222182111711</v>
+        <v>0.1207929269727917</v>
       </c>
     </row>
     <row r="34">
@@ -1883,13 +1883,13 @@
         <v>6.780104979292171</v>
       </c>
       <c r="I34" t="n">
-        <v>0.023775170831032</v>
+        <v>0.02860716509716501</v>
       </c>
       <c r="J34" t="n">
-        <v>0.03108691939109254</v>
+        <v>0.02161621062947185</v>
       </c>
       <c r="K34" t="n">
-        <v>0.124285589048738</v>
+        <v>0.1337562978103587</v>
       </c>
     </row>
     <row r="35">
@@ -1926,13 +1926,13 @@
         <v>6.786512127625599</v>
       </c>
       <c r="I35" t="n">
-        <v>0.023775170831032</v>
+        <v>0.02860716509716501</v>
       </c>
       <c r="J35" t="n">
-        <v>0.03116903208934941</v>
+        <v>0.02169832332772871</v>
       </c>
       <c r="K35" t="n">
-        <v>0.1243677017469949</v>
+        <v>0.1338384105086156</v>
       </c>
     </row>
     <row r="36">
@@ -1969,13 +1969,13 @@
         <v>6.773552910378499</v>
       </c>
       <c r="I36" t="n">
-        <v>0.023775170831032</v>
+        <v>0.02860716509716501</v>
       </c>
       <c r="J36" t="n">
-        <v>0.03445885423345741</v>
+        <v>0.02498814547183671</v>
       </c>
       <c r="K36" t="n">
-        <v>0.1276575238911029</v>
+        <v>0.1371282326527236</v>
       </c>
     </row>
     <row r="37">
@@ -2012,13 +2012,13 @@
         <v>6.762874755721914</v>
       </c>
       <c r="I37" t="n">
-        <v>0.023775170831032</v>
+        <v>0.02860716509716501</v>
       </c>
       <c r="J37" t="n">
-        <v>0.03801349075612071</v>
+        <v>0.02854278199450001</v>
       </c>
       <c r="K37" t="n">
-        <v>0.1312121604137662</v>
+        <v>0.1406828691753869</v>
       </c>
     </row>
     <row r="38">
@@ -2055,13 +2055,13 @@
         <v>6.779893131165665</v>
       </c>
       <c r="I38" t="n">
-        <v>0.023775170831032</v>
+        <v>0.02860716509716501</v>
       </c>
       <c r="J38" t="n">
-        <v>0.03079499896990013</v>
+        <v>0.02132429020827943</v>
       </c>
       <c r="K38" t="n">
-        <v>0.1239936686275456</v>
+        <v>0.1334643773891663</v>
       </c>
     </row>
     <row r="39">
@@ -2098,13 +2098,13 @@
         <v>6.777213173440835</v>
       </c>
       <c r="I39" t="n">
-        <v>0.023775170831032</v>
+        <v>0.02860716509716501</v>
       </c>
       <c r="J39" t="n">
-        <v>0.02911695805114901</v>
+        <v>0.01964624928952831</v>
       </c>
       <c r="K39" t="n">
-        <v>0.1223156277087944</v>
+        <v>0.1317863364704152</v>
       </c>
     </row>
     <row r="40">
@@ -2141,13 +2141,13 @@
         <v>6.774573791669479</v>
       </c>
       <c r="I40" t="n">
-        <v>0.023775170831032</v>
+        <v>0.02860716509716501</v>
       </c>
       <c r="J40" t="n">
-        <v>0.03024825631750461</v>
+        <v>0.02077754755588392</v>
       </c>
       <c r="K40" t="n">
-        <v>0.1234469259751501</v>
+        <v>0.1329176347367708</v>
       </c>
     </row>
     <row r="41">
@@ -2184,13 +2184,13 @@
         <v>6.741461528590615</v>
       </c>
       <c r="I41" t="n">
-        <v>0.023775170831032</v>
+        <v>0.02860716509716501</v>
       </c>
       <c r="J41" t="n">
-        <v>0.04067744788494943</v>
+        <v>0.03120673912332873</v>
       </c>
       <c r="K41" t="n">
-        <v>0.1338761175425949</v>
+        <v>0.1433468263042156</v>
       </c>
     </row>
     <row r="42">
@@ -2227,13 +2227,13 @@
         <v>6.724206067579491</v>
       </c>
       <c r="I42" t="n">
-        <v>0.023775170831032</v>
+        <v>0.02860716509716501</v>
       </c>
       <c r="J42" t="n">
-        <v>0.03721332321541949</v>
+        <v>0.02774261445379879</v>
       </c>
       <c r="K42" t="n">
-        <v>0.1304119928730649</v>
+        <v>0.1398827016346856</v>
       </c>
     </row>
     <row r="43">
@@ -2270,13 +2270,13 @@
         <v>6.706270733121253</v>
       </c>
       <c r="I43" t="n">
-        <v>0.023775170831032</v>
+        <v>0.02860716509716501</v>
       </c>
       <c r="J43" t="n">
-        <v>0.04007849715899359</v>
+        <v>0.0306077883973729</v>
       </c>
       <c r="K43" t="n">
-        <v>0.133277166816639</v>
+        <v>0.1427478755782597</v>
       </c>
     </row>
     <row r="44">
@@ -2313,13 +2313,13 @@
         <v>6.734098000710415</v>
       </c>
       <c r="I44" t="n">
-        <v>0.023775170831032</v>
+        <v>0.02860716509716501</v>
       </c>
       <c r="J44" t="n">
-        <v>0.03597633175237314</v>
+        <v>0.02650562299075244</v>
       </c>
       <c r="K44" t="n">
-        <v>0.1291750014100186</v>
+        <v>0.1386457101716393</v>
       </c>
     </row>
     <row r="45">
@@ -2356,13 +2356,13 @@
         <v>6.756865399212114</v>
       </c>
       <c r="I45" t="n">
-        <v>0.023775170831032</v>
+        <v>0.02860716509716501</v>
       </c>
       <c r="J45" t="n">
-        <v>0.04039298632946609</v>
+        <v>0.03092227756784539</v>
       </c>
       <c r="K45" t="n">
-        <v>0.1335916559871115</v>
+        <v>0.1430623647487322</v>
       </c>
     </row>
     <row r="46">
@@ -2399,13 +2399,13 @@
         <v>6.738006495406657</v>
       </c>
       <c r="I46" t="n">
-        <v>0.023775170831032</v>
+        <v>0.02860716509716501</v>
       </c>
       <c r="J46" t="n">
-        <v>0.04928795699792966</v>
+        <v>0.03981724823630896</v>
       </c>
       <c r="K46" t="n">
-        <v>0.1424866266555751</v>
+        <v>0.1519573354171958</v>
       </c>
     </row>
     <row r="47">
@@ -2442,13 +2442,13 @@
         <v>6.74310740535934</v>
       </c>
       <c r="I47" t="n">
-        <v>0.023775170831032</v>
+        <v>0.02860716509716501</v>
       </c>
       <c r="J47" t="n">
-        <v>0.04952771986721883</v>
+        <v>0.04005701110559813</v>
       </c>
       <c r="K47" t="n">
-        <v>0.1427263895248643</v>
+        <v>0.152197098286485</v>
       </c>
     </row>
     <row r="48">
@@ -2485,13 +2485,13 @@
         <v>6.732968250423442</v>
       </c>
       <c r="I48" t="n">
-        <v>0.023775170831032</v>
+        <v>0.02860716509716501</v>
       </c>
       <c r="J48" t="n">
-        <v>0.05816173570138284</v>
+        <v>0.04869102693976214</v>
       </c>
       <c r="K48" t="n">
-        <v>0.1513604053590283</v>
+        <v>0.160831114120649</v>
       </c>
     </row>
     <row r="49">
@@ -2528,13 +2528,13 @@
         <v>6.729910181438982</v>
       </c>
       <c r="I49" t="n">
-        <v>0.023775170831032</v>
+        <v>0.02860716509716501</v>
       </c>
       <c r="J49" t="n">
-        <v>0.05719083405950909</v>
+        <v>0.0477201252978884</v>
       </c>
       <c r="K49" t="n">
-        <v>0.1503895037171545</v>
+        <v>0.1598602124787752</v>
       </c>
     </row>
     <row r="50">
@@ -2571,13 +2571,13 @@
         <v>6.741895706671492</v>
       </c>
       <c r="I50" t="n">
-        <v>0.023775170831032</v>
+        <v>0.02860716509716501</v>
       </c>
       <c r="J50" t="n">
-        <v>0.05413819115163433</v>
+        <v>0.04466748239001363</v>
       </c>
       <c r="K50" t="n">
-        <v>0.1473368608092798</v>
+        <v>0.1568075695709005</v>
       </c>
     </row>
     <row r="51">
@@ -2614,13 +2614,13 @@
         <v>6.734431556692429</v>
       </c>
       <c r="I51" t="n">
-        <v>0.023775170831032</v>
+        <v>0.02860716509716501</v>
       </c>
       <c r="J51" t="n">
-        <v>0.0659313457069548</v>
+        <v>0.05646063694533411</v>
       </c>
       <c r="K51" t="n">
-        <v>0.1591300153646003</v>
+        <v>0.168600724126221</v>
       </c>
     </row>
     <row r="52">
@@ -2657,13 +2657,13 @@
         <v>6.726260387671091</v>
       </c>
       <c r="I52" t="n">
-        <v>0.023775170831032</v>
+        <v>0.02860716509716501</v>
       </c>
       <c r="J52" t="n">
-        <v>0.0689922096857345</v>
+        <v>0.0595215009241138</v>
       </c>
       <c r="K52" t="n">
-        <v>0.1621908793433799</v>
+        <v>0.1716615881050007</v>
       </c>
     </row>
     <row r="53">
@@ -2700,13 +2700,13 @@
         <v>6.689848076031109</v>
       </c>
       <c r="I53" t="n">
-        <v>0.023775170831032</v>
+        <v>0.02860716509716501</v>
       </c>
       <c r="J53" t="n">
-        <v>0.07658305846549784</v>
+        <v>0.06711234970387715</v>
       </c>
       <c r="K53" t="n">
-        <v>0.1697817281231433</v>
+        <v>0.179252436884764</v>
       </c>
     </row>
     <row r="54">
@@ -2743,13 +2743,13 @@
         <v>6.676075412416227</v>
       </c>
       <c r="I54" t="n">
-        <v>0.023775170831032</v>
+        <v>0.02860716509716501</v>
       </c>
       <c r="J54" t="n">
-        <v>0.07778334611047932</v>
+        <v>0.06831263734885863</v>
       </c>
       <c r="K54" t="n">
-        <v>0.1709820157681248</v>
+        <v>0.1804527245297455</v>
       </c>
     </row>
     <row r="55">
@@ -2786,13 +2786,13 @@
         <v>6.663659716321614</v>
       </c>
       <c r="I55" t="n">
-        <v>0.023775170831032</v>
+        <v>0.02860716509716501</v>
       </c>
       <c r="J55" t="n">
-        <v>0.07973219862280279</v>
+        <v>0.07026148986118209</v>
       </c>
       <c r="K55" t="n">
-        <v>0.1729308682804482</v>
+        <v>0.1824015770420689</v>
       </c>
     </row>
     <row r="56">
@@ -2829,13 +2829,13 @@
         <v>6.689169577841492</v>
       </c>
       <c r="I56" t="n">
-        <v>0.023775170831032</v>
+        <v>0.02860716509716501</v>
       </c>
       <c r="J56" t="n">
-        <v>0.08563658118787854</v>
+        <v>0.07616587242625784</v>
       </c>
       <c r="K56" t="n">
-        <v>0.178835250845524</v>
+        <v>0.1883059596071447</v>
       </c>
     </row>
     <row r="57">
@@ -2872,13 +2872,13 @@
         <v>6.711158072789449</v>
       </c>
       <c r="I57" t="n">
-        <v>0.023775170831032</v>
+        <v>0.02860716509716501</v>
       </c>
       <c r="J57" t="n">
-        <v>0.08632577053406032</v>
+        <v>0.07685506177243963</v>
       </c>
       <c r="K57" t="n">
-        <v>0.1795244401917058</v>
+        <v>0.1889951489533265</v>
       </c>
     </row>
     <row r="58">
@@ -2915,13 +2915,13 @@
         <v>6.690328392176552</v>
       </c>
       <c r="I58" t="n">
-        <v>0.023775170831032</v>
+        <v>0.02860716509716501</v>
       </c>
       <c r="J58" t="n">
-        <v>0.1028301427927343</v>
+        <v>0.09335943403111359</v>
       </c>
       <c r="K58" t="n">
-        <v>0.1960288124503797</v>
+        <v>0.2054995212120004</v>
       </c>
     </row>
     <row r="59">
@@ -2958,13 +2958,13 @@
         <v>6.696640714886168</v>
       </c>
       <c r="I59" t="n">
-        <v>0.023775170831032</v>
+        <v>0.02860716509716501</v>
       </c>
       <c r="J59" t="n">
-        <v>0.09893767014173727</v>
+        <v>0.08946696138011657</v>
       </c>
       <c r="K59" t="n">
-        <v>0.1921363397993827</v>
+        <v>0.2016070485610034</v>
       </c>
     </row>
     <row r="60">
@@ -3001,13 +3001,13 @@
         <v>6.686251051535382</v>
       </c>
       <c r="I60" t="n">
-        <v>0.023775170831032</v>
+        <v>0.02860716509716501</v>
       </c>
       <c r="J60" t="n">
-        <v>0.1068636900112818</v>
+        <v>0.09739298124966113</v>
       </c>
       <c r="K60" t="n">
-        <v>0.2000623596689273</v>
+        <v>0.209533068430548</v>
       </c>
     </row>
     <row r="61">
@@ -3044,13 +3044,13 @@
         <v>6.688228171679967</v>
       </c>
       <c r="I61" t="n">
-        <v>0.023775170831032</v>
+        <v>0.02860716509716501</v>
       </c>
       <c r="J61" t="n">
-        <v>0.09960563864680272</v>
+        <v>0.09013492988518203</v>
       </c>
       <c r="K61" t="n">
-        <v>0.1928043083044482</v>
+        <v>0.2022750170660689</v>
       </c>
     </row>
     <row r="62">
@@ -3087,13 +3087,13 @@
         <v>6.685622799336057</v>
       </c>
       <c r="I62" t="n">
-        <v>0.023775170831032</v>
+        <v>0.02860716509716501</v>
       </c>
       <c r="J62" t="n">
-        <v>0.1085967338902114</v>
+        <v>0.09912602512859071</v>
       </c>
       <c r="K62" t="n">
-        <v>0.2017954035478569</v>
+        <v>0.2112661123094776</v>
       </c>
     </row>
     <row r="63">
@@ -3130,13 +3130,13 @@
         <v>6.689270749001296</v>
       </c>
       <c r="I63" t="n">
-        <v>0.023775170831032</v>
+        <v>0.02860716509716501</v>
       </c>
       <c r="J63" t="n">
-        <v>0.108632337004843</v>
+        <v>0.09916162824322229</v>
       </c>
       <c r="K63" t="n">
-        <v>0.2018310066624884</v>
+        <v>0.2113017154241091</v>
       </c>
     </row>
     <row r="64">
@@ -3173,13 +3173,13 @@
         <v>6.679500555685947</v>
       </c>
       <c r="I64" t="n">
-        <v>0.023775170831032</v>
+        <v>0.02860716509716501</v>
       </c>
       <c r="J64" t="n">
-        <v>0.1252148584432178</v>
+        <v>0.1157441496815971</v>
       </c>
       <c r="K64" t="n">
-        <v>0.2184135281008632</v>
+        <v>0.2278842368624839</v>
       </c>
     </row>
   </sheetData>
